--- a/E/CLP03N.xlsx
+++ b/E/CLP03N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="287">
   <si>
     <t/>
   </si>
@@ -88,6 +88,15 @@
     <t>BF QUICK BIT ODENG60</t>
   </si>
   <si>
+    <t>20143394</t>
+  </si>
+  <si>
+    <t>BF QCKBIT SPCY BBQ50</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>20137694</t>
   </si>
   <si>
@@ -130,9 +139,6 @@
     <t>CEDEA CRB STIK SPC50</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>20138974</t>
   </si>
   <si>
@@ -701,9 +707,6 @@
   </si>
   <si>
     <t>16</t>
-  </si>
-  <si>
-    <t>TG,(E-3H)</t>
   </si>
   <si>
     <t>20142608</t>
@@ -1261,7 +1264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F128"/>
+  <dimension ref="A1:F129"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1462,10 +1465,10 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>6</v>
@@ -1473,10 +1476,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1485,7 +1488,7 @@
         <v>17</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>6</v>
@@ -1493,10 +1496,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1505,7 +1508,7 @@
         <v>17</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>6</v>
@@ -1513,10 +1516,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1525,7 +1528,7 @@
         <v>17</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>6</v>
@@ -1533,10 +1536,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1545,7 +1548,7 @@
         <v>17</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>6</v>
@@ -1553,10 +1556,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1565,7 +1568,7 @@
         <v>17</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>6</v>
@@ -1573,10 +1576,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1585,7 +1588,7 @@
         <v>17</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>6</v>
@@ -1602,21 +1605,21 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1625,10 +1628,10 @@
         <v>20</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1645,10 +1648,10 @@
         <v>20</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1665,10 +1668,10 @@
         <v>20</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1685,10 +1688,10 @@
         <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1702,13 +1705,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F22" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1725,10 +1728,10 @@
         <v>5</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1745,10 +1748,10 @@
         <v>5</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1765,10 +1768,10 @@
         <v>5</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1785,10 +1788,10 @@
         <v>5</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1805,10 +1808,10 @@
         <v>5</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1822,13 +1825,13 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F28" s="1" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1845,7 +1848,7 @@
         <v>9</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>6</v>
@@ -1865,7 +1868,7 @@
         <v>9</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>6</v>
@@ -1885,7 +1888,7 @@
         <v>9</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>6</v>
@@ -1905,10 +1908,10 @@
         <v>9</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1925,10 +1928,10 @@
         <v>9</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1942,13 +1945,13 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1962,10 +1965,10 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>6</v>
@@ -1982,10 +1985,10 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>6</v>
@@ -2002,10 +2005,10 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>6</v>
@@ -2022,10 +2025,10 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>6</v>
@@ -2042,10 +2045,10 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>6</v>
@@ -2062,10 +2065,10 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>6</v>
@@ -2073,19 +2076,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="C41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="E41" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>6</v>
@@ -2102,10 +2105,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>6</v>
@@ -2122,10 +2125,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>6</v>
@@ -2142,10 +2145,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>6</v>
@@ -2162,10 +2165,10 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>6</v>
@@ -2182,33 +2185,33 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="C47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2222,30 +2225,30 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>6</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="E49" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>6</v>
@@ -2262,10 +2265,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -2282,13 +2285,13 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2302,13 +2305,13 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2322,13 +2325,13 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>6</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2342,10 +2345,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>6</v>
@@ -2362,10 +2365,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>6</v>
@@ -2382,10 +2385,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>6</v>
@@ -2402,10 +2405,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>6</v>
@@ -2413,19 +2416,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>6</v>
@@ -2433,42 +2436,42 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="C59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F59" s="1" t="s">
-        <v>132</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2482,13 +2485,13 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2502,13 +2505,13 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2522,13 +2525,13 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2542,13 +2545,13 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>6</v>
+        <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2562,10 +2565,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>6</v>
@@ -2582,10 +2585,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>6</v>
@@ -2602,10 +2605,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>6</v>
@@ -2622,10 +2625,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>6</v>
@@ -2642,10 +2645,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>6</v>
@@ -2662,53 +2665,53 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>155</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="C71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2722,13 +2725,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2742,13 +2745,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2762,13 +2765,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2782,13 +2785,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>6</v>
+        <v>160</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2802,53 +2805,53 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>172</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="E78" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F78" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2862,13 +2865,13 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2882,33 +2885,33 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2922,13 +2925,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>6</v>
+        <v>184</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2942,7 +2945,7 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>5</v>
@@ -2962,10 +2965,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>6</v>
@@ -2982,10 +2985,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>6</v>
@@ -3002,10 +3005,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>6</v>
@@ -3022,33 +3025,33 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>4</v>
+        <v>109</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>175</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="C89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="E89" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3062,13 +3065,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>6</v>
+        <v>177</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3082,10 +3085,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>6</v>
@@ -3102,10 +3105,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>6</v>
@@ -3122,10 +3125,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>6</v>
@@ -3142,10 +3145,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>6</v>
@@ -3153,19 +3156,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="E95" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>6</v>
@@ -3182,10 +3185,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>6</v>
@@ -3202,10 +3205,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>6</v>
@@ -3222,13 +3225,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>175</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3242,13 +3245,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3262,33 +3265,33 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>224</v>
+        <v>177</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="E101" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3302,70 +3305,70 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>230</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>6</v>
+        <v>226</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>6</v>
@@ -3373,19 +3376,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>6</v>
@@ -3393,19 +3396,19 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>6</v>
@@ -3413,99 +3416,99 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>224</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>6</v>
+        <v>226</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>6</v>
@@ -3513,19 +3516,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>109</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>6</v>
@@ -3533,19 +3536,19 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>6</v>
@@ -3553,19 +3556,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>6</v>
@@ -3573,19 +3576,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>6</v>
@@ -3593,19 +3596,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>6</v>
@@ -3613,19 +3616,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>6</v>
@@ -3633,19 +3636,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>6</v>
@@ -3653,19 +3656,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>6</v>
@@ -3673,19 +3676,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>6</v>
@@ -3693,19 +3696,19 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>6</v>
@@ -3713,19 +3716,19 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="E123" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>6</v>
@@ -3733,19 +3736,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>6</v>
@@ -3753,19 +3756,19 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>6</v>
@@ -3773,19 +3776,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>6</v>
@@ -3793,19 +3796,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>6</v>
@@ -3813,22 +3816,42 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>224</v>
+      <c r="B129" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>
